--- a/manufacturing_forms/001_gearbox_design_feedback_form--manufacturing_forms.xlsx
+++ b/manufacturing_forms/001_gearbox_design_feedback_form--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>manufacturability_attachment</t>
+          <t>assembly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manufacturability Attachment</t>
+          <t>Assembly</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,40 +653,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>durability</t>
+          <t>reliability</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Durability</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>manufacturability_attachment</t>
+          <t>maintainability</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Manufacturability Attachment</t>
+          <t>Maintainability</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,40 +699,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assembly</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assembly</t>
+          <t>Overall Satisfaction</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>manufacturability_attachment</t>
+          <t>design_forces</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manufacturability Attachment</t>
+          <t>Design Forces</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,23 +745,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>reliability</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>manufacturability_attachment</t>
+          <t>attachment_design</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manufacturability Attachment</t>
+          <t>Attachment (Design)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,23 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maintainability</t>
+          <t>attachment_assembly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>Attachment (Assembly)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,269 +819,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>manufacturability_attachment</t>
+          <t>attachment_reliability</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Manufacturability Attachment</t>
+          <t>Attachment (Reliability)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>manufacturability_attachment</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Manufacturability Attachment</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>overall_satisfaction</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Overall Satisfaction</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>manufacturability_attachment</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Manufacturability Attachment</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>design_forces</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Design Forces</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>manufacturability_attachment</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Manufacturability Attachment</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>manufacturability_attachment</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Manufacturability Attachment</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>manufacturability_attachment</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Manufacturability Attachment</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>manufacturability_attachment</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Manufacturability Attachment</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>manufacturability_attachment</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Manufacturability Attachment</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>manufacturability_attachment</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Manufacturability Attachment</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1262,75 +1009,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>durability_choices</t>
+          <t>reliability_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Very Good</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>durability_choices</t>
+          <t>reliability_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>durability_choices</t>
+          <t>reliability_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>durability_choices</t>
+          <t>reliability_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>reliability_choices</t>
+          <t>maintainability_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1094,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>reliability_choices</t>
+          <t>maintainability_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1111,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>reliability_choices</t>
+          <t>maintainability_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1128,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>reliability_choices</t>
+          <t>maintainability_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1145,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>maintainability_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1162,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>maintainability_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1179,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>maintainability_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1196,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>maintainability_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1213,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>overall_satisfaction_choices</t>
+          <t>design_forces_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1230,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>overall_satisfaction_choices</t>
+          <t>design_forces_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1247,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>overall_satisfaction_choices</t>
+          <t>design_forces_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1264,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>overall_satisfaction_choices</t>
+          <t>design_forces_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1526,74 +1273,6 @@
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>design_forces_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>design_forces_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>design_forces_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>design_forces_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>Not Applicable</t>
         </is>
